--- a/data/dividends_info_20260717.xlsx
+++ b/data/dividends_info_20260717.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>51.97000122070312</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1731768287204638</v>
+        <v>0.1672862477254513</v>
       </c>
       <c r="J2" t="n">
         <v>241</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.15000152587891</v>
+        <v>63.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.091192491581799</v>
+        <v>1.095461632683227</v>
       </c>
       <c r="J3" t="n">
         <v>220</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.199999809265137</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6521739265643809</v>
+        <v>0.6550218449725329</v>
       </c>
       <c r="J4" t="n">
         <v>150</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>51.9900016784668</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1731102079138346</v>
+        <v>0.1672862477254513</v>
       </c>
       <c r="J6" t="n">
         <v>150</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.150000095367432</v>
+        <v>2.144999980926514</v>
       </c>
       <c r="I7" t="n">
-        <v>3.58139518997746</v>
+        <v>3.589743621663835</v>
       </c>
       <c r="J7" t="n">
         <v>129</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.39500045776367</v>
+        <v>21.64500045776367</v>
       </c>
       <c r="I8" t="n">
-        <v>1.261977070451636</v>
+        <v>1.24740122102033</v>
       </c>
       <c r="J8" t="n">
         <v>129</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.099999904632568</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>3.278688575849199</v>
+        <v>3.305785019747363</v>
       </c>
       <c r="J9" t="n">
         <v>122</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>7.050000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.8510638067620513</v>
       </c>
       <c r="J10" t="n">
         <v>94</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.900000095367432</v>
+        <v>4.909999847412109</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7755101889880786</v>
+        <v>0.7739307776155733</v>
       </c>
       <c r="J13" t="n">
         <v>73</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.39500045776367</v>
+        <v>21.64500045776367</v>
       </c>
       <c r="I14" t="n">
-        <v>1.261977070451636</v>
+        <v>1.24740122102033</v>
       </c>
       <c r="J14" t="n">
         <v>66</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>51.9900016784668</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1731102079138346</v>
+        <v>0.1672862477254513</v>
       </c>
       <c r="J15" t="n">
         <v>66</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92.5</v>
+        <v>90.09999847412109</v>
       </c>
       <c r="I16" t="n">
-        <v>1.437837837837838</v>
+        <v>1.476137649860237</v>
       </c>
       <c r="J16" t="n">
         <v>66</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.539999961853027</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="I17" t="n">
-        <v>5.415162492161021</v>
+        <v>5.434782627474683</v>
       </c>
       <c r="J17" t="n">
         <v>59</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4.900000095367432</v>
+        <v>4.909999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7755101889880786</v>
+        <v>0.7739307776155733</v>
       </c>
       <c r="J19" t="n">
         <v>17</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.799999952316284</v>
+        <v>2.769999980926514</v>
       </c>
       <c r="I20" t="n">
-        <v>5.284607232853467</v>
+        <v>5.34184119201716</v>
       </c>
       <c r="J20" t="n">
         <v>17</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.71999979019165</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="I21" t="n">
-        <v>4.370629530943106</v>
+        <v>4.340277605310641</v>
       </c>
       <c r="J21" t="n">
         <v>10</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4.199999809265137</v>
+        <v>4.230000019073486</v>
       </c>
       <c r="I22" t="n">
-        <v>3.333333484710216</v>
+        <v>3.30969265647107</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>10.18000030517578</v>
+        <v>10.16800022125244</v>
       </c>
       <c r="I23" t="n">
-        <v>2.554027428347022</v>
+        <v>2.557041643808841</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>14.10000038146973</v>
+        <v>13.9399995803833</v>
       </c>
       <c r="I24" t="n">
-        <v>4.255319033810256</v>
+        <v>4.30416081822796</v>
       </c>
       <c r="J24" t="n">
         <v>3</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.848000049591064</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="I25" t="n">
-        <v>7.724718966616209</v>
+        <v>7.829181654088743</v>
       </c>
       <c r="J25" t="n">
         <v>3</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6.869999885559082</v>
+        <v>6.965000152587891</v>
       </c>
       <c r="I27" t="n">
-        <v>1.455604099938962</v>
+        <v>1.435750148014632</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>19.35000038146973</v>
+        <v>19.54999923706055</v>
       </c>
       <c r="I28" t="n">
-        <v>1.943152416472671</v>
+        <v>1.923273732344829</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.710000038146973</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I30" t="n">
-        <v>2.101576168096538</v>
+        <v>2.105263228341595</v>
       </c>
       <c r="J30" t="n">
         <v>-4</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3.019999980926514</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I32" t="n">
-        <v>4.966887448588033</v>
+        <v>5.03355701476259</v>
       </c>
       <c r="J32" t="n">
         <v>-4</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.180000066757202</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I33" t="n">
-        <v>3.899082449407415</v>
+        <v>3.971962422114281</v>
       </c>
       <c r="J33" t="n">
         <v>-11</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4.5</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="I34" t="n">
-        <v>1.555555555555556</v>
+        <v>1.580135501410437</v>
       </c>
       <c r="J34" t="n">
         <v>-11</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4225352112676056</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="J35" t="n">
         <v>-11</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J37" t="n">
         <v>-18</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>22.07999992370605</v>
+        <v>22.15999984741211</v>
       </c>
       <c r="I38" t="n">
-        <v>4.30253624675079</v>
+        <v>4.287003639627475</v>
       </c>
       <c r="J38" t="n">
         <v>-25</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>27.64999961853027</v>
+        <v>28.04999923706055</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7052441326954534</v>
+        <v>0.6951871846839832</v>
       </c>
       <c r="J39" t="n">
         <v>-25</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.899999976158142</v>
+        <v>1.884999990463257</v>
       </c>
       <c r="I40" t="n">
-        <v>1.736842127057654</v>
+        <v>1.75066313883057</v>
       </c>
       <c r="J40" t="n">
         <v>-25</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>5.054999828338623</v>
+        <v>5.065000057220459</v>
       </c>
       <c r="I41" t="n">
-        <v>5.73689435901151</v>
+        <v>5.725567556244895</v>
       </c>
       <c r="J41" t="n">
         <v>-25</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.930000066757202</v>
+        <v>3.927999973297119</v>
       </c>
       <c r="I42" t="n">
-        <v>4.071246750181923</v>
+        <v>4.073319783291592</v>
       </c>
       <c r="J42" t="n">
         <v>-25</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.546000003814697</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I43" t="n">
-        <v>5.443833456101109</v>
+        <v>5.41406262101373</v>
       </c>
       <c r="J43" t="n">
         <v>-25</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>49.79999923706055</v>
+        <v>50.75</v>
       </c>
       <c r="I44" t="n">
-        <v>1.265060260344666</v>
+        <v>1.241379310344828</v>
       </c>
       <c r="J44" t="n">
         <v>-25</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6.184999942779541</v>
+        <v>6.164999961853027</v>
       </c>
       <c r="I45" t="n">
-        <v>2.263540845516709</v>
+        <v>2.270884036760317</v>
       </c>
       <c r="J45" t="n">
         <v>-25</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>27.81999969482422</v>
+        <v>27.84000015258789</v>
       </c>
       <c r="I47" t="n">
-        <v>3.055355892610375</v>
+        <v>3.0531609028062</v>
       </c>
       <c r="J47" t="n">
         <v>-25</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>51.9900016784668</v>
+        <v>53.79999923706055</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1731102079138346</v>
+        <v>0.1672862477254513</v>
       </c>
       <c r="J48" t="n">
         <v>-25</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.480000019073486</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6756756669679118</v>
+        <v>0.6849314889533817</v>
       </c>
       <c r="J49" t="n">
         <v>-25</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.230000019073486</v>
+        <v>6.223999977111816</v>
       </c>
       <c r="I50" t="n">
-        <v>2.910112350641093</v>
+        <v>2.912917748501188</v>
       </c>
       <c r="J50" t="n">
         <v>-25</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>9.420000076293945</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I51" t="n">
-        <v>2.760084903335693</v>
+        <v>2.765957559056285</v>
       </c>
       <c r="J51" t="n">
         <v>-25</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10.28499984741211</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I52" t="n">
-        <v>2.693242626247566</v>
+        <v>2.676328403774081</v>
       </c>
       <c r="J52" t="n">
         <v>-25</v>
@@ -2896,7 +2896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4058,7 +4058,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CASTELLO SGR S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4092,7 +4092,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4109,7 +4109,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4143,7 +4143,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4160,7 +4160,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>CASTELLO SGR S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4177,7 +4177,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4204,14 +4204,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4255,14 +4255,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4279,7 +4279,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4374,14 +4374,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4391,14 +4391,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4459,14 +4459,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4517,7 +4517,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4551,7 +4551,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4561,14 +4561,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4595,14 +4595,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4619,7 +4619,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4629,14 +4629,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4663,14 +4663,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4680,14 +4680,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4697,14 +4697,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4714,14 +4714,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4772,7 +4772,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4799,14 +4799,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4816,14 +4816,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4833,14 +4833,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4850,14 +4850,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4884,14 +4884,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4908,7 +4908,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5010,7 +5010,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5037,14 +5037,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5054,14 +5054,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5071,14 +5071,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5088,14 +5088,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5105,14 +5105,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5146,12 +5146,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5163,97 +5163,97 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5265,58 +5265,58 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5350,7 +5350,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5360,14 +5360,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5384,7 +5384,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5394,14 +5394,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5411,14 +5411,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5428,70 +5428,70 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5503,12 +5503,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5520,12 +5520,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5537,12 +5537,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5554,97 +5554,97 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5656,29 +5656,29 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5690,12 +5690,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5707,24 +5707,24 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5741,7 +5741,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5775,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5785,19 +5785,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5809,29 +5809,29 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5843,12 +5843,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5860,12 +5860,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5877,63 +5877,63 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5945,12 +5945,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5962,7 +5962,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5979,7 +5979,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6013,7 +6013,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6064,7 +6064,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6081,7 +6081,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6091,36 +6091,36 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6132,12 +6132,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6149,12 +6149,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6166,12 +6166,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6183,92 +6183,92 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6329,14 +6329,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6346,14 +6346,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6363,14 +6363,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6387,29 +6387,29 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6421,219 +6421,49 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Neodecortech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
         <is>
           <t>Half Year Preliminary Results</t>
         </is>
@@ -6650,104 +6480,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sesa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004729759</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.437837837837838</v>
-      </c>
-      <c r="I2" t="n">
-        <v>66</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6758,95 +6493,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Lottomatica Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Unipol S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>